--- a/tests/workbooktests/workbooks/test_termstructures.xlsx
+++ b/tests/workbooktests/workbooks/test_termstructures.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F3B37E-9393-4E07-8DDD-CC865D001488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B041EF9C-348B-4751-AFDB-4AF10402FB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="-20235" windowWidth="28800" windowHeight="18120" activeTab="1" xr2:uid="{AB19F68A-3F3A-4039-9EC4-FD0D0D1E9554}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{AB19F68A-3F3A-4039-9EC4-FD0D0D1E9554}"/>
   </bookViews>
   <sheets>
     <sheet name="YieldTermStructure" sheetId="1" r:id="rId1"/>
@@ -170,10 +170,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -199,10 +206,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,9 +604,9 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="str" cm="1">
-        <f t="array" ref="C9">_xll.qlFlatForward(C2,C3,C4,C5,C6,C7)</f>
-        <v>欣[test_termstructures.xlsx]YieldTermStructure!R9C3YieldTermStructureHandle,A</v>
+      <c r="C9" t="e" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">_xll.qlFlatForward(C2,C3,C4,C5,C6,C7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
@@ -623,180 +631,171 @@
       <c r="B14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" t="str" cm="1">
-        <f t="array" ref="C14">_xll.qlTermStructureDayCounter(C9)</f>
-        <v>Actual/365 (Fixed)</v>
+      <c r="C14" t="e" cm="1">
+        <f t="array" aca="1" ref="C14" ca="1">_xll.qlTermStructureDayCounter(C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" cm="1">
-        <f t="array" ref="C15">_xll.qlTermStructureTimeFromReference(C9,C11)</f>
-        <v>1</v>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlTermStructureTimeFromReference(C9,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="str" cm="1">
-        <f t="array" ref="C16">_xll.qlTermStructureCalendar(C9)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no calendar implementation provided
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\calendars.py", line 94, in xCalendar
-    return calendar.name()
-           ~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 2746, in name
-    return _QuantLib.Calendar_name(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no calendar implementation provided
-</v>
+      <c r="C16" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">FIND("RuntimeError: RuntimeError: no calendar implementation provided", _xll.qlTermStructureCalendar(C9))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" cm="1">
-        <f t="array" ref="C17">_xll.qlTermStructureReferenceDate(C9)</f>
-        <v>45658</v>
+      <c r="C17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlTermStructureReferenceDate(C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="1" cm="1">
-        <f t="array" ref="C18">_xll.qlTermStructureMaxDate(C9)</f>
-        <v>109574</v>
+      <c r="C18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlTermStructureMaxDate(C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="2" cm="1">
-        <f t="array" ref="C19">_xll.qlTermStructureMaxTime(C9)</f>
-        <v>175.1123287671233</v>
+      <c r="C19" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C19" ca="1">_xll.qlTermStructureMaxTime(C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>20</v>
       </c>
-      <c r="C20" t="b" cm="1">
-        <f t="array" ref="C20">_xll.qlTermStructureAllowsExtrapolation(C9)</f>
-        <v>0</v>
+      <c r="C20" t="e" cm="1">
+        <f t="array" aca="1" ref="C20" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="b" cm="1">
-        <f t="array" ref="C21">_xll.qlTermStructureEnableExrapolation(C9,C20)</f>
-        <v>1</v>
+      <c r="C21" t="e" cm="1">
+        <f t="array" aca="1" ref="C21" ca="1">_xll.qlTermStructureEnableExrapolation(C9,C20)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="b" cm="1">
-        <f t="array" ref="C22">_xll.qlTermStructureAllowsExtrapolation(C9,C21)</f>
-        <v>1</v>
+      <c r="C22" t="e" cm="1">
+        <f t="array" aca="1" ref="C22" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9,C21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>19</v>
       </c>
-      <c r="C23" t="b" cm="1">
-        <f t="array" ref="C23">_xll.qlTermStructureDisableExrapolation(C9,C22)</f>
-        <v>1</v>
+      <c r="C23" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlTermStructureDisableExrapolation(C9,C22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>20</v>
       </c>
-      <c r="C24" t="b" cm="1">
-        <f t="array" ref="C24">_xll.qlTermStructureAllowsExtrapolation(C9,C23)</f>
-        <v>0</v>
+      <c r="C24" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9,C23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="C26" cm="1">
-        <f t="array" ref="C26">_xll.qlYieldTermStructureDiscount(C9,C11)</f>
-        <v>0.970873786407767</v>
+      <c r="C26" t="e" cm="1">
+        <f t="array" aca="1" ref="C26" ca="1">_xll.qlYieldTermStructureDiscount(C9,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>23</v>
       </c>
-      <c r="C27" cm="1">
-        <f t="array" ref="C27">_xll.qlYieldTermStructureDiscountFromTime(C9,C15)</f>
-        <v>0.970873786407767</v>
+      <c r="C27" t="e" cm="1">
+        <f t="array" aca="1" ref="C27" ca="1">_xll.qlYieldTermStructureDiscountFromTime(C9,C15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>24</v>
       </c>
-      <c r="C28" cm="1">
-        <f t="array" ref="C28">_xll.qlYieldTermStructureZeroRate(C9,C11,C4,C5,C6)</f>
-        <v>3.0000000000000027E-2</v>
+      <c r="C28" t="e" cm="1">
+        <f t="array" aca="1" ref="C28" ca="1">_xll.qlYieldTermStructureZeroRate(C9,C11,C4,C5,C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" cm="1">
-        <f t="array" ref="C29">_xll.qlYieldTermStructureZeroRateFromTime(C9,C15,C5,C6)</f>
-        <v>3.0000000000000027E-2</v>
+      <c r="C29" t="e" cm="1">
+        <f t="array" aca="1" ref="C29" ca="1">_xll.qlYieldTermStructureZeroRateFromTime(C9,C15,C5,C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>26</v>
       </c>
-      <c r="C30" cm="1">
-        <f t="array" ref="C30">_xll.qlYieldTermStructureForwardRate(C9,C11,C12,C4,C5,C6)</f>
-        <v>3.0000000000000027E-2</v>
+      <c r="C30" t="e" cm="1">
+        <f t="array" aca="1" ref="C30" ca="1">_xll.qlYieldTermStructureForwardRate(C9,C11,C12,C4,C5,C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>27</v>
       </c>
-      <c r="C31" cm="1">
-        <f t="array" ref="C31">_xll.qlYieldTermStructureForwardRateFromTime(C9,C15,C15,C5,C6)</f>
-        <v>2.9999999998685745E-2</v>
+      <c r="C31" t="e" cm="1">
+        <f t="array" aca="1" ref="C31" ca="1">_xll.qlYieldTermStructureForwardRateFromTime(C9,C15,C15,C5,C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>28</v>
       </c>
-      <c r="C33" t="str" cm="1">
-        <f t="array" ref="C33">_xll.qlImpliedTermStructure(C9,C11)</f>
-        <v>欣[test_termstructures.xlsx]YieldTermStructure!R33C3YieldTermStructureHandle,A</v>
+      <c r="C33" t="e" cm="1">
+        <f t="array" aca="1" ref="C33" ca="1">_xll.qlImpliedTermStructure(C9,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>22</v>
       </c>
-      <c r="C34" cm="1">
-        <f t="array" ref="C34">_xll.qlYieldTermStructureDiscount(C33,C11)</f>
-        <v>1</v>
+      <c r="C34" t="e" cm="1">
+        <f t="array" aca="1" ref="C34" ca="1">_xll.qlYieldTermStructureDiscount(C33,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -873,90 +872,90 @@
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" t="str" cm="1">
-        <f t="array" ref="C10">_xll.qlFlatForward(C2,C3,C5,C6,C7,C8)</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R10C3YieldTermStructureHandle,A</v>
+      <c r="C10" t="e" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_xll.qlFlatForward(C2,C3,C5,C6,C7,C8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="str" cm="1">
-        <f t="array" ref="C12">_xll.qlZeroSpreadedTermStructure(C10,C4,C6,C7,C5)</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R12C3YieldTermStructureHandle,A</v>
+      <c r="C12" t="e" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">_xll.qlZeroSpreadedTermStructure(C10,C4,C6,C7,C5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" cm="1">
-        <f t="array" ref="C13">_xll.qlYieldTermStructureZeroRate(C12,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>4.0000000000000036E-2</v>
+      <c r="C13" t="e" cm="1">
+        <f t="array" aca="1" ref="C13" ca="1">_xll.qlYieldTermStructureZeroRate(C12,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="str" cm="1">
-        <f t="array" ref="C15">_xll.qlForwardSpreadedTermStructure(C10,C4)</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R15C3YieldTermStructureHandle,A</v>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlForwardSpreadedTermStructure(C10,C4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" cm="1">
-        <f t="array" ref="C16">_xll.qlYieldTermStructureZeroRate(C15,C2+365,C5,C6,C7)</f>
-        <v>4.0351672096692992E-2</v>
+      <c r="C16" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">_xll.qlYieldTermStructureZeroRate(C15,C2+365,C5,C6,C7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="str" cm="1">
-        <f t="array" ref="C18">_xll.qlFlatForward(C2,C4,C5,C6,C7,C8)</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R18C3YieldTermStructureHandle,A</v>
+      <c r="C18" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlFlatForward(C2,C4,C5,C6,C7,C8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="str" cm="1">
-        <f t="array" ref="C20">_xll.qlCompositeZeroYieldStructure(C10,C18,"+")</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R20C3YieldTermStructureHandle,A</v>
+      <c r="C20" t="e" cm="1">
+        <f t="array" aca="1" ref="C20" ca="1">_xll.qlCompositeZeroYieldStructure(C10,C18,"+")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" cm="1">
-        <f t="array" ref="C21">_xll.qlYieldTermStructureZeroRate(C20,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>4.0300000000000002E-2</v>
+      <c r="C21" t="e" cm="1">
+        <f t="array" aca="1" ref="C21" ca="1">_xll.qlYieldTermStructureZeroRate(C20,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>33</v>
       </c>
-      <c r="C23" t="str" cm="1">
-        <f t="array" ref="C23">_xll.qlCompositeZeroYieldStructure(C10,C18,"-")</f>
-        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R23C3YieldTermStructureHandle,A</v>
+      <c r="C23" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlCompositeZeroYieldStructure(C10,C18,"-")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" cm="1">
-        <f t="array" ref="C24">_xll.qlYieldTermStructureZeroRate(C23,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>1.980198019801982E-2</v>
+      <c r="C24" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlYieldTermStructureZeroRate(C23,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
